--- a/new-info14/web.xlsx
+++ b/new-info14/web.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\object\projectInfo\new-info14\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="15270" windowHeight="8805"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>domain</t>
   </si>
@@ -40,25 +45,16 @@
     <t>color2</t>
   </si>
   <si>
-    <t>apricitys.fun</t>
-  </si>
-  <si>
-    <t>#c2849f</t>
-  </si>
-  <si>
-    <t>#eba46f</t>
-  </si>
-  <si>
-    <t>halcyons.top</t>
-  </si>
-  <si>
-    <t>#746097</t>
-  </si>
-  <si>
-    <t>nescience.cloud</t>
-  </si>
-  <si>
-    <t>#dc7067</t>
+    <t>read.roaddivider.cloud</t>
+  </si>
+  <si>
+    <t>#a48ce6</t>
+  </si>
+  <si>
+    <t>sec.roaddivider.cloud</t>
+  </si>
+  <si>
+    <t>#373834</t>
   </si>
   <si>
     <t>#f7ece7</t>
@@ -67,40 +63,31 @@
     <t>#a37070</t>
   </si>
   <si>
-    <t>fleetings.cloud</t>
-  </si>
-  <si>
-    <t>#f0cfe3</t>
-  </si>
-  <si>
     <t>#e2e1dd</t>
   </si>
   <si>
     <t>#4167b1</t>
   </si>
   <si>
-    <t>oneirics.site</t>
-  </si>
-  <si>
     <t>#fafbe6</t>
   </si>
   <si>
     <t>#d62828</t>
   </si>
   <si>
+    <t>#c6e6e8</t>
+  </si>
+  <si>
+    <t>#e58889</t>
+  </si>
+  <si>
+    <t>#e3e3e5</t>
+  </si>
+  <si>
+    <t>#b57743</t>
+  </si>
+  <si>
     <t>#f5f4f7</t>
-  </si>
-  <si>
-    <t>#c6e6e8</t>
-  </si>
-  <si>
-    <t>#e58889</t>
-  </si>
-  <si>
-    <t>#e3e3e5</t>
-  </si>
-  <si>
-    <t>#b57743</t>
   </si>
   <si>
     <t>#a61b29</t>
@@ -116,7 +103,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="29">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -127,16 +114,50 @@
     <font>
       <u/>
       <sz val="10"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF2972F4"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
       <name val="Helvetica"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -146,26 +167,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Microsoft YaHei"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Microsoft YaHei"/>
@@ -316,7 +317,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="50">
+  <fills count="52">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -325,25 +326,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA48CE6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBA46F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF373834"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC2849F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEBA46F"/>
+        <fgColor rgb="FFDC7067"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF746097"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC7067"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -721,28 +734,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -751,43 +755,46 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -799,130 +806,145 @@
     <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1332,107 +1354,78 @@
       <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>5</v>
-      </c>
+      <c r="C2" s="3"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
+      <c r="C3" s="5"/>
     </row>
     <row r="4" ht="16.5" spans="1:10">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="6"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="8"/>
+      <c r="I4" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4" s="10" t="s">
         <v>8</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:10">
-      <c r="A5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="6" t="s">
+      <c r="A5" s="11"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="7"/>
+      <c r="I5" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>15</v>
+      <c r="J5" s="14" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:10">
-      <c r="A6" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J6" s="14" t="s">
-        <v>18</v>
+      <c r="A6" s="11"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="12"/>
+      <c r="I6" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="J6" s="17" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:10">
-      <c r="B7" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="12"/>
-      <c r="I7" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="J7" s="17" t="s">
-        <v>21</v>
+      <c r="B7" s="18"/>
+      <c r="C7" s="15"/>
+      <c r="I7" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7" s="20" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:10">
-      <c r="B8" s="16"/>
-      <c r="I8" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="J8" s="19" t="s">
-        <v>23</v>
+      <c r="B8" s="19"/>
+      <c r="I8" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8" s="22" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="I9" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="J9" s="12" t="s">
-        <v>24</v>
+      <c r="I9" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" display="apricitys.fun"/>
-    <hyperlink ref="A3" r:id="rId2" display="halcyons.top"/>
-    <hyperlink ref="A4" r:id="rId3" display="nescience.cloud"/>
-    <hyperlink ref="A5" r:id="rId4" display="fleetings.cloud"/>
-    <hyperlink ref="A6" r:id="rId5" display="oneirics.site"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
